--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D593"/>
+  <dimension ref="A1:D595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9922,6 +9922,38 @@
         <v>2604.49</v>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>6</v>
+      </c>
+      <c r="C594" t="n">
+        <v>363</v>
+      </c>
+      <c r="D594" t="n">
+        <v>2745.78</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>8</v>
+      </c>
+      <c r="C595" t="n">
+        <v>364</v>
+      </c>
+      <c r="D595" t="n">
+        <v>2900.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D595"/>
+  <dimension ref="A1:D596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9954,6 +9954,22 @@
         <v>2900.07</v>
       </c>
     </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>5</v>
+      </c>
+      <c r="C596" t="n">
+        <v>374</v>
+      </c>
+      <c r="D596" t="n">
+        <v>3031.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D596"/>
+  <dimension ref="A1:D597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9970,6 +9970,22 @@
         <v>3031.23</v>
       </c>
     </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>4</v>
+      </c>
+      <c r="C597" t="n">
+        <v>367</v>
+      </c>
+      <c r="D597" t="n">
+        <v>2797.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D597"/>
+  <dimension ref="A1:D598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9986,6 +9986,22 @@
         <v>2797.24</v>
       </c>
     </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>13</v>
+      </c>
+      <c r="C598" t="n">
+        <v>370</v>
+      </c>
+      <c r="D598" t="n">
+        <v>2905.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D598"/>
+  <dimension ref="A1:D599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10002,6 +10002,22 @@
         <v>2905.51</v>
       </c>
     </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>9</v>
+      </c>
+      <c r="C599" t="n">
+        <v>392</v>
+      </c>
+      <c r="D599" t="n">
+        <v>2694.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D599"/>
+  <dimension ref="A1:D601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10018,6 +10018,38 @@
         <v>2694.75</v>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>4</v>
+      </c>
+      <c r="C600" t="n">
+        <v>399</v>
+      </c>
+      <c r="D600" t="n">
+        <v>3006.49</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>12</v>
+      </c>
+      <c r="C601" t="n">
+        <v>395</v>
+      </c>
+      <c r="D601" t="n">
+        <v>3252.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D601"/>
+  <dimension ref="A1:D602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10050,6 +10050,22 @@
         <v>3252.07</v>
       </c>
     </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>7</v>
+      </c>
+      <c r="C602" t="n">
+        <v>407</v>
+      </c>
+      <c r="D602" t="n">
+        <v>3590.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D602"/>
+  <dimension ref="A1:D603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10066,6 +10066,22 @@
         <v>3590.21</v>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>3</v>
+      </c>
+      <c r="C603" t="n">
+        <v>382</v>
+      </c>
+      <c r="D603" t="n">
+        <v>3201.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D603"/>
+  <dimension ref="A1:D604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10082,6 +10082,22 @@
         <v>3201.95</v>
       </c>
     </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>8</v>
+      </c>
+      <c r="C604" t="n">
+        <v>405</v>
+      </c>
+      <c r="D604" t="n">
+        <v>3324.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D604"/>
+  <dimension ref="A1:D605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10098,6 +10098,22 @@
         <v>3324.73</v>
       </c>
     </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>5</v>
+      </c>
+      <c r="C605" t="n">
+        <v>395</v>
+      </c>
+      <c r="D605" t="n">
+        <v>3083.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D605"/>
+  <dimension ref="A1:D606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10114,6 +10114,22 @@
         <v>3083.15</v>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>5</v>
+      </c>
+      <c r="C606" t="n">
+        <v>406</v>
+      </c>
+      <c r="D606" t="n">
+        <v>3198.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D606"/>
+  <dimension ref="A1:D608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10130,6 +10130,38 @@
         <v>3198.51</v>
       </c>
     </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>3</v>
+      </c>
+      <c r="C607" t="n">
+        <v>423</v>
+      </c>
+      <c r="D607" t="n">
+        <v>3285.29</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>2</v>
+      </c>
+      <c r="C608" t="n">
+        <v>380</v>
+      </c>
+      <c r="D608" t="n">
+        <v>3376.32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D608"/>
+  <dimension ref="A1:D609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10162,6 +10162,22 @@
         <v>3376.32</v>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>5</v>
+      </c>
+      <c r="C609" t="n">
+        <v>395</v>
+      </c>
+      <c r="D609" t="n">
+        <v>3511.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D609"/>
+  <dimension ref="A1:D610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10178,6 +10178,22 @@
         <v>3511.65</v>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>4</v>
+      </c>
+      <c r="C610" t="n">
+        <v>386</v>
+      </c>
+      <c r="D610" t="n">
+        <v>3691.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D610"/>
+  <dimension ref="A1:D611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10194,6 +10194,22 @@
         <v>3691.36</v>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>4</v>
+      </c>
+      <c r="C611" t="n">
+        <v>387</v>
+      </c>
+      <c r="D611" t="n">
+        <v>3387.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D611"/>
+  <dimension ref="A1:D612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10210,6 +10210,22 @@
         <v>3387.33</v>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>10</v>
+      </c>
+      <c r="C612" t="n">
+        <v>409</v>
+      </c>
+      <c r="D612" t="n">
+        <v>3216.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D612"/>
+  <dimension ref="A1:D613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10226,6 +10226,22 @@
         <v>3216.01</v>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>4</v>
+      </c>
+      <c r="C613" t="n">
+        <v>395</v>
+      </c>
+      <c r="D613" t="n">
+        <v>3517.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D613"/>
+  <dimension ref="A1:D614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10242,6 +10242,22 @@
         <v>3517.14</v>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>3</v>
+      </c>
+      <c r="C614" t="n">
+        <v>371</v>
+      </c>
+      <c r="D614" t="n">
+        <v>3370.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D614"/>
+  <dimension ref="A1:D617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10258,6 +10258,54 @@
         <v>3370.78</v>
       </c>
     </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>2</v>
+      </c>
+      <c r="C615" t="n">
+        <v>366</v>
+      </c>
+      <c r="D615" t="n">
+        <v>3353.56</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>4</v>
+      </c>
+      <c r="C616" t="n">
+        <v>358</v>
+      </c>
+      <c r="D616" t="n">
+        <v>3649.88</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>1</v>
+      </c>
+      <c r="C617" t="n">
+        <v>357</v>
+      </c>
+      <c r="D617" t="n">
+        <v>3447.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D617"/>
+  <dimension ref="A1:D618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10306,6 +10306,22 @@
         <v>3447.48</v>
       </c>
     </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>6</v>
+      </c>
+      <c r="C618" t="n">
+        <v>338</v>
+      </c>
+      <c r="D618" t="n">
+        <v>3094.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D618"/>
+  <dimension ref="A1:D619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10322,6 +10322,22 @@
         <v>3094.62</v>
       </c>
     </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>3</v>
+      </c>
+      <c r="C619" t="n">
+        <v>345</v>
+      </c>
+      <c r="D619" t="n">
+        <v>3068.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D619"/>
+  <dimension ref="A1:D620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10338,6 +10338,22 @@
         <v>3068.54</v>
       </c>
     </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>3</v>
+      </c>
+      <c r="C620" t="n">
+        <v>365</v>
+      </c>
+      <c r="D620" t="n">
+        <v>3075.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D620"/>
+  <dimension ref="A1:D621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10354,6 +10354,22 @@
         <v>3075.63</v>
       </c>
     </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>5</v>
+      </c>
+      <c r="C621" t="n">
+        <v>367</v>
+      </c>
+      <c r="D621" t="n">
+        <v>2871.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D621"/>
+  <dimension ref="A1:D623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10370,6 +10370,38 @@
         <v>2871.8</v>
       </c>
     </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>8</v>
+      </c>
+      <c r="C622" t="n">
+        <v>351</v>
+      </c>
+      <c r="D622" t="n">
+        <v>2659.21</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>7</v>
+      </c>
+      <c r="C623" t="n">
+        <v>354</v>
+      </c>
+      <c r="D623" t="n">
+        <v>2632.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D623"/>
+  <dimension ref="A1:D624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10402,6 +10402,22 @@
         <v>2632.49</v>
       </c>
     </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>4</v>
+      </c>
+      <c r="C624" t="n">
+        <v>371</v>
+      </c>
+      <c r="D624" t="n">
+        <v>3075.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D624"/>
+  <dimension ref="A1:D625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10418,6 +10418,22 @@
         <v>3075.58</v>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>4</v>
+      </c>
+      <c r="C625" t="n">
+        <v>357</v>
+      </c>
+      <c r="D625" t="n">
+        <v>2652.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D625"/>
+  <dimension ref="A1:D626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10434,6 +10434,22 @@
         <v>2652.61</v>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>5</v>
+      </c>
+      <c r="C626" t="n">
+        <v>356</v>
+      </c>
+      <c r="D626" t="n">
+        <v>2648.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D626"/>
+  <dimension ref="A1:D627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10450,6 +10450,22 @@
         <v>2648.99</v>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>1</v>
+      </c>
+      <c r="C627" t="n">
+        <v>363</v>
+      </c>
+      <c r="D627" t="n">
+        <v>2805.64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D627"/>
+  <dimension ref="A1:D628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10466,6 +10466,22 @@
         <v>2805.64</v>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>3</v>
+      </c>
+      <c r="C628" t="n">
+        <v>371</v>
+      </c>
+      <c r="D628" t="n">
+        <v>2872.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D628"/>
+  <dimension ref="A1:D630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10482,6 +10482,38 @@
         <v>2872.1</v>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>7</v>
+      </c>
+      <c r="C629" t="n">
+        <v>380</v>
+      </c>
+      <c r="D629" t="n">
+        <v>2937.85</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>1</v>
+      </c>
+      <c r="C630" t="n">
+        <v>390</v>
+      </c>
+      <c r="D630" t="n">
+        <v>3395.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D630"/>
+  <dimension ref="A1:D631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10514,6 +10514,22 @@
         <v>3395.8</v>
       </c>
     </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>5</v>
+      </c>
+      <c r="C631" t="n">
+        <v>378</v>
+      </c>
+      <c r="D631" t="n">
+        <v>3331.17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D631"/>
+  <dimension ref="A1:D632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10530,6 +10530,22 @@
         <v>3331.17</v>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>7</v>
+      </c>
+      <c r="C632" t="n">
+        <v>371</v>
+      </c>
+      <c r="D632" t="n">
+        <v>2784.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D632"/>
+  <dimension ref="A1:D633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10546,6 +10546,22 @@
         <v>2784.58</v>
       </c>
     </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>9</v>
+      </c>
+      <c r="C633" t="n">
+        <v>378</v>
+      </c>
+      <c r="D633" t="n">
+        <v>2776.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D633"/>
+  <dimension ref="A1:D634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10562,6 +10562,22 @@
         <v>2776.7</v>
       </c>
     </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>8</v>
+      </c>
+      <c r="C634" t="n">
+        <v>367</v>
+      </c>
+      <c r="D634" t="n">
+        <v>2793.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D634"/>
+  <dimension ref="A1:D635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10578,6 +10578,22 @@
         <v>2793.72</v>
       </c>
     </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>7</v>
+      </c>
+      <c r="C635" t="n">
+        <v>383</v>
+      </c>
+      <c r="D635" t="n">
+        <v>2781.15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D635"/>
+  <dimension ref="A1:D637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10594,6 +10594,38 @@
         <v>2781.15</v>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>8</v>
+      </c>
+      <c r="C636" t="n">
+        <v>394</v>
+      </c>
+      <c r="D636" t="n">
+        <v>2820.12</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>1</v>
+      </c>
+      <c r="C637" t="n">
+        <v>396</v>
+      </c>
+      <c r="D637" t="n">
+        <v>3114.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D637"/>
+  <dimension ref="A1:D638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10626,6 +10626,22 @@
         <v>3114.53</v>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>7</v>
+      </c>
+      <c r="C638" t="n">
+        <v>399</v>
+      </c>
+      <c r="D638" t="n">
+        <v>3190.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D638"/>
+  <dimension ref="A1:D639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10642,6 +10642,22 @@
         <v>3190.31</v>
       </c>
     </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>3</v>
+      </c>
+      <c r="C639" t="n">
+        <v>361</v>
+      </c>
+      <c r="D639" t="n">
+        <v>2450.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D639"/>
+  <dimension ref="A1:D640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10658,6 +10658,22 @@
         <v>2450.13</v>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>0</v>
+      </c>
+      <c r="C640" t="n">
+        <v>367</v>
+      </c>
+      <c r="D640" t="n">
+        <v>2712.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D640"/>
+  <dimension ref="A1:D641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10674,6 +10674,22 @@
         <v>2712.4</v>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>10</v>
+      </c>
+      <c r="C641" t="n">
+        <v>364</v>
+      </c>
+      <c r="D641" t="n">
+        <v>2607.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/美团数据.xlsx
+++ b/美团数据.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D641"/>
+  <dimension ref="A1:D642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10690,6 +10690,22 @@
         <v>2607.68</v>
       </c>
     </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>10</v>
+      </c>
+      <c r="C642" t="n">
+        <v>390</v>
+      </c>
+      <c r="D642" t="n">
+        <v>2834.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
